--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486433_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486433_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8436</v>
+        <v>5.9112</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3652</v>
+        <v>3.1416</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4785</v>
+        <v>2.7695</v>
       </c>
       <c r="G2" t="n">
         <v>2.6914</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3273</v>
+        <v>1.3949</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7006</v>
+        <v>0.4771</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6267</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>2.2599</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1127</v>
+        <v>4.8756</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6387</v>
+        <v>4.0405</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5261</v>
+        <v>0.835</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3</v>
+        <v>3.5801</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0427</v>
+        <v>1.0094</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3427</v>
+        <v>2.5707</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1703</v>
+        <v>2.7093</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6387</v>
+        <v>0.5657</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5316</v>
+        <v>2.1436</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8703</v>
+        <v>0.8708</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6814</v>
+        <v>0.4437</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1889</v>
+        <v>0.4271</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.512</v>
+        <v>1.1007</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.399</v>
+        <v>0.6814</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1131</v>
+        <v>0.4194</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7597</v>
+        <v>1.4997</v>
       </c>
       <c r="W3" t="n">
-        <v>3.9549</v>
+        <v>2.8249</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8467</v>
+        <v>4.5703</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2582</v>
+        <v>4.819</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5884</v>
+        <v>-0.2487</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5801</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0094</v>
+        <v>-0.0427</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5707</v>
+        <v>1.3427</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7093</v>
+        <v>2.1703</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5657</v>
+        <v>0.6387</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1436</v>
+        <v>1.5316</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8708</v>
+        <v>-0.8703</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4437</v>
+        <v>-0.6814</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4271</v>
+        <v>-0.1889</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.0544</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1009</v>
+        <v>-0.2187</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1728</v>
+        <v>0.1643</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4997</v>
+        <v>3.7597</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8249</v>
+        <v>3.9549</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6847</v>
+        <v>3.996</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3479</v>
+        <v>3.7517</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3368</v>
+        <v>0.2444</v>
       </c>
       <c r="G5" t="n">
         <v>3.3196</v>
@@ -844,13 +844,13 @@
         <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8649</v>
+        <v>1.1762</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7246</v>
+        <v>1.1284</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1402</v>
+        <v>0.0478</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9347</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0015</v>
+        <v>3.5401</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4089</v>
+        <v>2.7009</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5926</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3734</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0274</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1815</v>
+        <v>0.1106</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2088</v>
+        <v>0.4554</v>
       </c>
       <c r="V6" t="n">
         <v>2.2599</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0086</v>
+        <v>2.0964</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7453</v>
+        <v>0.9256</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2633</v>
+        <v>1.1709</v>
       </c>
       <c r="G7" t="n">
         <v>2.8666</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2073</v>
+        <v>1.2951</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4266</v>
+        <v>0.6069</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.6883</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7602</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8521</v>
+        <v>0.5004</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0686</v>
+        <v>-0.2661</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2165</v>
+        <v>0.7665</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.748</v>
+        <v>0.6291</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0218</v>
+        <v>-0.7543</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7698</v>
+        <v>1.3833</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3343</v>
+        <v>1.2324</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.1063</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4319</v>
+        <v>1.3387</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5863</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9242</v>
+        <v>-0.6479</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3379</v>
+        <v>0.0446</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8823</v>
+        <v>-0.0634</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0777</v>
+        <v>-0.411</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1954</v>
+        <v>0.3476</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9347</v>
+        <v>0.3698</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2599</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.271</v>
+        <v>0.4581</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4031</v>
+        <v>1.243</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6741</v>
+        <v>-0.785</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6291</v>
+        <v>-0.748</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7543</v>
+        <v>1.0218</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3833</v>
+        <v>-1.7698</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2324</v>
+        <v>-1.3343</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1063</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3387</v>
+        <v>-1.4319</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6032999999999999</v>
+        <v>0.5863</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6479</v>
+        <v>0.9242</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0446</v>
+        <v>-0.3379</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2929</v>
+        <v>1.4883</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.548</v>
+        <v>1.2522</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2551</v>
+        <v>0.2361</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3698</v>
+        <v>-0.9347</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3698</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0033</v>
+        <v>0.1029</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9987</v>
+        <v>-0.8617</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9954</v>
+        <v>0.9646</v>
       </c>
       <c r="G10" t="n">
         <v>2.3561</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.62</v>
+        <v>0.7261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1406</v>
+        <v>0.2776</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4793</v>
+        <v>0.4485</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6743</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1246</v>
+        <v>-0.873</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7805</v>
+        <v>-1.159</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6559</v>
+        <v>0.286</v>
       </c>
       <c r="G11" t="n">
         <v>1.3838</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2964</v>
+        <v>0.548</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2776</v>
+        <v>-0.1009</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0188</v>
+        <v>0.6489</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4997</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>24.493</v>
+        <v>25.178</v>
       </c>
       <c r="E12" t="n">
-        <v>17.6505</v>
+        <v>18.3355</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8424</v>
+        <v>6.842399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>17.0053</v>
@@ -1360,7 +1360,7 @@
         <v>9.032499999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>7.972499999999998</v>
+        <v>7.9725</v>
       </c>
       <c r="J12" t="n">
         <v>17.0027</v>
@@ -1390,13 +1390,13 @@
         <v>7.612500000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>7.4926</v>
+        <v>8.177499999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1183</v>
+        <v>3.8036</v>
       </c>
       <c r="U12" t="n">
-        <v>4.3739</v>
+        <v>4.3741</v>
       </c>
       <c r="V12" t="n">
         <v>4.345400000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9516</v>
+        <v>3.0267</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8977</v>
+        <v>2.5566</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0538</v>
+        <v>0.4701</v>
       </c>
       <c r="G13" t="n">
         <v>2.2803</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>0.519</v>
+        <v>-0.4059</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6187</v>
+        <v>0.2776</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0997</v>
+        <v>-0.6835</v>
       </c>
       <c r="V13" t="n">
         <v>0.9347</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5158</v>
+        <v>0.7168</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2422</v>
+        <v>3.5716</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7264</v>
+        <v>-2.8548</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3461</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1441</v>
+        <v>0.3452</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1887</v>
+        <v>-0.4819</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9555</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3698</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7798</v>
+        <v>-0.6865</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9094</v>
+        <v>-0.6331</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6893</v>
+        <v>-0.0534</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9224</v>
+        <v>-1.6637</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5048</v>
+        <v>0.3436</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4272</v>
+        <v>-2.0073</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4794</v>
+        <v>-0.1464</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1862</v>
+        <v>0.6935</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7068</v>
+        <v>-0.8399</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4018</v>
+        <v>-1.5173</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6814</v>
+        <v>-0.3499</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7204</v>
+        <v>-1.1674</v>
       </c>
       <c r="P15" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8134</v>
+        <v>-0.2196</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3509</v>
+        <v>-0.4867</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4625</v>
+        <v>0.2671</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3491</v>
+        <v>0.5443</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7809</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1678</v>
+        <v>-0.7863</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7025</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4653</v>
+        <v>-1.3604</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9435</v>
+        <v>-0.9224</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3012</v>
+        <v>0.5048</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6423</v>
+        <v>-1.4272</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3601</v>
+        <v>0.4794</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3467</v>
+        <v>1.1862</v>
       </c>
       <c r="L16" t="n">
         <v>-0.7068</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5834</v>
+        <v>-1.4018</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6479</v>
+        <v>-0.6814</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0645</v>
+        <v>-0.7204</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8769</v>
+        <v>-0.8199</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3425</v>
+        <v>-0.6862</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5344</v>
+        <v>-0.1337</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.7809</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4123</v>
+        <v>-0.9263</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9683</v>
+        <v>-0.7025</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4439</v>
+        <v>-0.2238</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6637</v>
+        <v>-0.9435</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3436</v>
+        <v>-0.3012</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0073</v>
+        <v>-0.6423</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1464</v>
+        <v>-0.3601</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6935</v>
+        <v>0.3467</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8399</v>
+        <v>-0.7068</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5173</v>
+        <v>-0.5834</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3499</v>
+        <v>-0.6479</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1674</v>
+        <v>0.0645</v>
       </c>
       <c r="P17" t="n">
         <v>0.6525</v>
@@ -1780,22 +1780,22 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9454</v>
+        <v>-0.6354</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>-0.3425</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1234</v>
+        <v>-0.2929</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4149</v>
+        <v>-1.7444</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7236</v>
+        <v>-1.5001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6913</v>
+        <v>-0.2443</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3974</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1921</v>
+        <v>-0.5215</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7126</v>
+        <v>-0.2656</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3904</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5351</v>
+        <v>-2.0251</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9295</v>
+        <v>-2.5943</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3944</v>
+        <v>0.5692</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0009</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6218</v>
+        <v>-0.1118</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0053</v>
+        <v>0.1694</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0219</v>
+        <v>-3.1982</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7865</v>
+        <v>-1.0483</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2354</v>
+        <v>-2.1499</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8234</v>
+        <v>-1.613</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.9197</v>
+        <v>-2.1198</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0.5068</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2111</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3259</v>
+        <v>-0.392</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1147</v>
+        <v>1.2272</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6123</v>
+        <v>-2.4482</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5939</v>
+        <v>-1.7278</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0184</v>
+        <v>-0.7204</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4606</v>
+        <v>-0.3455</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4879</v>
+        <v>-0.4687</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0273</v>
+        <v>0.1232</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3904</v>
+        <v>-0.3698</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.24</v>
+        <v>-3.8536</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6071</v>
+        <v>-2.6748</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6329</v>
+        <v>-1.1789</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.613</v>
+        <v>-3.8234</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1198</v>
+        <v>-2.9197</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5068</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8352000000000001</v>
+        <v>-1.2111</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.392</v>
+        <v>-1.3259</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2272</v>
+        <v>0.1147</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4482</v>
+        <v>-2.6123</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7278</v>
+        <v>-1.5939</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7204</v>
+        <v>-1.0184</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3872</v>
+        <v>-0.2923</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0274</v>
+        <v>-0.3761</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3598</v>
+        <v>0.0838</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3698</v>
+        <v>-0.3904</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.985</v>
+        <v>-5.4698</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3228</v>
+        <v>-2.9875</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6622</v>
+        <v>-2.4824</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6048</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.055</v>
+        <v>-0.5399</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.822</v>
+        <v>-0.4867</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.233</v>
+        <v>-0.0532</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4035</v>
+        <v>-6.566</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8514</v>
+        <v>-1.4044</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.5521</v>
+        <v>-5.1616</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9704</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8034</v>
+        <v>-0.9659</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2329</v>
+        <v>-0.7859</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5705</v>
+        <v>-0.18</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6297</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.4929</v>
+        <v>-21.5127</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8424</v>
+        <v>-6.8427</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.6506</v>
+        <v>-14.6702</v>
       </c>
       <c r="G24" t="n">
         <v>-17.0053</v>
@@ -2317,7 +2317,7 @@
         <v>-6.781499999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>4.35</v>
+        <v>4.350000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-7.6126</v>
@@ -2326,13 +2326,13 @@
         <v>11.9626</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.492699999999999</v>
+        <v>-4.512499999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.3742</v>
+        <v>-4.3743</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.1184</v>
+        <v>-0.1383000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3454</v>
